--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7162,0.0659,0.0234,0.1730</t>
-  </si>
-  <si>
-    <t>0.0229,0.0010,0.0005,0.9923</t>
-  </si>
-  <si>
-    <t>0.8764,0.0132,0.0132,0.0647</t>
-  </si>
-  <si>
-    <t>0.3440,0.0024,0.0023,0.8490</t>
-  </si>
-  <si>
-    <t>0.9976,0.0009,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9969,0.0005,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9923,0.0044,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9900,0.0009,0.0008,0.0045</t>
-  </si>
-  <si>
-    <t>0.9879,0.0193,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9902,0.0169,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0030,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0002,0.0000,0.0020</t>
-  </si>
-  <si>
-    <t>0.7062,0.0608,0.3023,0.0038</t>
-  </si>
-  <si>
-    <t>0.5186,0.0688,0.5047,0.0041</t>
-  </si>
-  <si>
-    <t>0.1790,0.0033,0.9327,0.0004</t>
-  </si>
-  <si>
-    <t>0.3208,0.0149,0.7811,0.0014</t>
-  </si>
-  <si>
-    <t>0.5141,0.4093,0.1177,0.0127</t>
-  </si>
-  <si>
-    <t>0.0753,0.9363,0.0037,0.0005</t>
-  </si>
-  <si>
-    <t>0.1563,0.8953,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.8492,0.2550,0.0050,0.0007</t>
-  </si>
-  <si>
-    <t>0.3957,0.7796,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.0123,0.9866,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.6465,0.0087,0.3498,0.0409</t>
-  </si>
-  <si>
-    <t>0.5845,0.0187,0.4715,0.0148</t>
-  </si>
-  <si>
-    <t>0.0324,0.0119,0.9380,0.0173</t>
-  </si>
-  <si>
-    <t>0.6014,0.0154,0.5123,0.0121</t>
-  </si>
-  <si>
-    <t>0.0973,0.0250,0.9388,0.0024</t>
-  </si>
-  <si>
-    <t>0.1061,0.0077,0.9299,0.0032</t>
-  </si>
-  <si>
-    <t>0.0130,0.0041,0.9875,0.0010</t>
-  </si>
-  <si>
-    <t>0.7912,0.3616,0.0079,0.0030</t>
-  </si>
-  <si>
-    <t>0.5199,0.1529,0.4316,0.0155</t>
-  </si>
-  <si>
-    <t>0.0386,0.0845,0.8927,0.0028</t>
-  </si>
-  <si>
-    <t>0.0094,0.9606,0.0447,0.0005</t>
-  </si>
-  <si>
-    <t>0.7686,0.1322,0.0527,0.0650</t>
-  </si>
-  <si>
-    <t>0.1930,0.7208,0.0762,0.0097</t>
-  </si>
-  <si>
-    <t>0.7945,0.3356,0.0086,0.0009</t>
-  </si>
-  <si>
-    <t>0.0115,0.9709,0.0668,0.0024</t>
-  </si>
-  <si>
-    <t>0.0234,0.8425,0.1266,0.0882</t>
-  </si>
-  <si>
-    <t>0.1835,0.0673,0.6773,0.1417</t>
-  </si>
-  <si>
-    <t>0.0913,0.2935,0.6230,0.0026</t>
-  </si>
-  <si>
-    <t>0.1752,0.0166,0.3899,0.4863</t>
-  </si>
-  <si>
-    <t>0.0403,0.2200,0.8822,0.0048</t>
-  </si>
-  <si>
-    <t>0.0039,0.9869,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.0764,0.1991,0.8172,0.0062</t>
-  </si>
-  <si>
-    <t>0.0613,0.5781,0.0595,0.7927</t>
-  </si>
-  <si>
-    <t>0.0018,0.9844,0.0155,0.0389</t>
-  </si>
-  <si>
-    <t>0.0034,0.9786,0.0398,0.0029</t>
-  </si>
-  <si>
-    <t>0.0025,0.9861,0.0544,0.0007</t>
-  </si>
-  <si>
-    <t>0.0229,0.4491,0.8830,0.0155</t>
-  </si>
-  <si>
-    <t>0.0039,0.2577,0.9738,0.0014</t>
-  </si>
-  <si>
-    <t>0.3940,0.0318,0.6022,0.0422</t>
-  </si>
-  <si>
-    <t>0.0579,0.0032,0.9734,0.0006</t>
-  </si>
-  <si>
-    <t>0.0026,0.0160,0.9898,0.0024</t>
-  </si>
-  <si>
-    <t>0.0487,0.0988,0.8746,0.0035</t>
-  </si>
-  <si>
-    <t>0.9654,0.0711,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9774,0.0119,0.0109,0.0015</t>
-  </si>
-  <si>
-    <t>0.7274,0.3448,0.0027,0.0055</t>
-  </si>
-  <si>
-    <t>0.0024,0.0821,0.9912,0.0004</t>
-  </si>
-  <si>
-    <t>0.9799,0.0220,0.0039,0.0009</t>
-  </si>
-  <si>
-    <t>0.9878,0.0144,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9678,0.0615,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0241,0.8194,0.6346,0.0049</t>
-  </si>
-  <si>
-    <t>0.0017,0.0744,0.9782,0.0084</t>
-  </si>
-  <si>
-    <t>0.0214,0.2116,0.9131,0.0173</t>
-  </si>
-  <si>
-    <t>0.0038,0.9564,0.6087,0.0008</t>
-  </si>
-  <si>
-    <t>0.0050,0.0525,0.9747,0.0062</t>
-  </si>
-  <si>
-    <t>0.0155,0.9442,0.0294,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9982,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7840,0.0846,0.1991,0.0049</t>
-  </si>
-  <si>
-    <t>0.1923,0.1259,0.7246,0.0036</t>
-  </si>
-  <si>
-    <t>0.0264,0.0921,0.9313,0.0004</t>
-  </si>
-  <si>
-    <t>0.0046,0.9402,0.4388,0.0013</t>
-  </si>
-  <si>
-    <t>0.0033,0.9082,0.7004,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.9944,0.0389,0.0001</t>
-  </si>
-  <si>
-    <t>0.0168,0.7995,0.5235,0.0030</t>
-  </si>
-  <si>
-    <t>0.2495,0.0092,0.0311,0.8026</t>
-  </si>
-  <si>
-    <t>0.0016,0.0019,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.0090,0.0034,0.0005,0.9952</t>
-  </si>
-  <si>
-    <t>0.0550,0.0103,0.0149,0.9649</t>
-  </si>
-  <si>
-    <t>0.0053,0.0145,0.0033,0.9942</t>
-  </si>
-  <si>
-    <t>0.0022,0.0037,0.0021,0.9972</t>
-  </si>
-  <si>
-    <t>0.0026,0.9431,0.5767,0.0006</t>
-  </si>
-  <si>
-    <t>0.0009,0.9064,0.9404,0.0005</t>
-  </si>
-  <si>
-    <t>0.0489,0.2103,0.8075,0.0082</t>
-  </si>
-  <si>
-    <t>0.0341,0.6732,0.6559,0.0035</t>
-  </si>
-  <si>
-    <t>0.0010,0.9795,0.0806,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.9088,0.5710,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0020,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9394,0.0692,0.0096,0.0019</t>
-  </si>
-  <si>
-    <t>0.9702,0.0359,0.0022,0.0010</t>
-  </si>
-  <si>
-    <t>0.9914,0.0019,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9879,0.0134,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9962,0.0007,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9879,0.0200,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9910,0.0142,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0003,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9949,0.0007,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.9971,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0025,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0014,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9949,0.0038,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9904,0.0032,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.0040,0.0083,0.9809,0.0100</t>
-  </si>
-  <si>
-    <t>0.0150,0.0100,0.9740,0.0040</t>
-  </si>
-  <si>
-    <t>0.5936,0.0138,0.5226,0.0051</t>
-  </si>
-  <si>
-    <t>0.1745,0.0151,0.8470,0.0041</t>
-  </si>
-  <si>
-    <t>0.0337,0.9552,0.0051,0.0020</t>
-  </si>
-  <si>
-    <t>0.1820,0.8614,0.0060,0.0023</t>
-  </si>
-  <si>
-    <t>0.2522,0.7774,0.0005,0.0037</t>
-  </si>
-  <si>
-    <t>0.5525,0.6365,0.0032,0.0009</t>
-  </si>
-  <si>
-    <t>0.4265,0.6993,0.0037,0.0040</t>
-  </si>
-  <si>
-    <t>0.0155,0.9774,0.0029,0.0002</t>
-  </si>
-  <si>
-    <t>0.9262,0.1449,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.6340,0.1902,0.2526,0.0302</t>
-  </si>
-  <si>
-    <t>0.2558,0.0428,0.7213,0.0378</t>
-  </si>
-  <si>
-    <t>0.1512,0.7644,0.0662,0.0437</t>
-  </si>
-  <si>
-    <t>0.3433,0.1270,0.5427,0.0116</t>
-  </si>
-  <si>
-    <t>0.0562,0.4845,0.0606,0.8492</t>
-  </si>
-  <si>
-    <t>0.0029,0.9896,0.0214,0.0005</t>
-  </si>
-  <si>
-    <t>0.0035,0.9700,0.0223,0.0860</t>
-  </si>
-  <si>
-    <t>0.0153,0.9356,0.0691,0.0380</t>
-  </si>
-  <si>
-    <t>0.0003,0.9879,0.4289,0.0009</t>
-  </si>
-  <si>
-    <t>0.0405,0.9573,0.0366,0.0006</t>
-  </si>
-  <si>
-    <t>0.6849,0.4652,0.0147,0.0054</t>
-  </si>
-  <si>
-    <t>0.7189,0.4681,0.0046,0.0016</t>
-  </si>
-  <si>
-    <t>0.9930,0.0046,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9756,0.0204,0.0040,0.0014</t>
-  </si>
-  <si>
-    <t>0.9882,0.0020,0.0010,0.0032</t>
-  </si>
-  <si>
-    <t>0.9792,0.0046,0.0024,0.0041</t>
-  </si>
-  <si>
-    <t>0.9893,0.0055,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9828,0.0178,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.9812,0.0144,0.0049,0.0010</t>
-  </si>
-  <si>
-    <t>0.9720,0.0247,0.0086,0.0010</t>
-  </si>
-  <si>
-    <t>0.0026,0.7473,0.8807,0.0037</t>
-  </si>
-  <si>
-    <t>0.0088,0.6553,0.7813,0.0007</t>
-  </si>
-  <si>
-    <t>0.0111,0.2200,0.9445,0.0032</t>
-  </si>
-  <si>
-    <t>0.0483,0.1483,0.8635,0.0028</t>
-  </si>
-  <si>
-    <t>0.7439,0.0866,0.1876,0.0208</t>
-  </si>
-  <si>
-    <t>0.5881,0.2692,0.1646,0.0196</t>
-  </si>
-  <si>
-    <t>0.5463,0.0061,0.6719,0.0047</t>
-  </si>
-  <si>
-    <t>0.5020,0.1986,0.3277,0.0063</t>
-  </si>
-  <si>
-    <t>0.0711,0.0006,0.0026,0.9726</t>
-  </si>
-  <si>
-    <t>0.0002,0.0068,0.0038,0.9988</t>
-  </si>
-  <si>
-    <t>0.0005,0.0306,0.0045,0.9973</t>
-  </si>
-  <si>
-    <t>0.0069,0.0016,0.0006,0.9960</t>
-  </si>
-  <si>
-    <t>0.0062,0.8702,0.7659,0.0022</t>
-  </si>
-  <si>
-    <t>0.9381,0.0791,0.0051,0.0016</t>
-  </si>
-  <si>
-    <t>0.4225,0.6908,0.0030,0.0015</t>
-  </si>
-  <si>
-    <t>0.9823,0.0105,0.0009,0.0013</t>
-  </si>
-  <si>
-    <t>0.9212,0.1352,0.0018,0.0005</t>
-  </si>
-  <si>
-    <t>0.9757,0.0067,0.0085,0.0028</t>
-  </si>
-  <si>
-    <t>0.4078,0.0559,0.0105,0.6561</t>
-  </si>
-  <si>
-    <t>0.9773,0.0162,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.0003,0.5574,0.8657,0.0680</t>
-  </si>
-  <si>
-    <t>0.8061,0.0054,0.0524,0.1083</t>
-  </si>
-  <si>
-    <t>0.5742,0.0017,0.0100,0.5292</t>
-  </si>
-  <si>
-    <t>0.4474,0.5535,0.0513,0.0073</t>
-  </si>
-  <si>
-    <t>0.8322,0.1255,0.0481,0.0048</t>
-  </si>
-  <si>
-    <t>0.9075,0.0650,0.0199,0.0036</t>
-  </si>
-  <si>
-    <t>0.1491,0.7596,0.0307,0.1018</t>
-  </si>
-  <si>
-    <t>0.8941,0.0807,0.0250,0.0041</t>
-  </si>
-  <si>
-    <t>0.7938,0.3038,0.0157,0.0019</t>
-  </si>
-  <si>
-    <t>0.9934,0.0019,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9897,0.0024,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9925,0.0012,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9894,0.0009,0.0003,0.0049</t>
-  </si>
-  <si>
-    <t>0.9735,0.0299,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.9851,0.0054,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.9936,0.0037,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9948,0.0001,0.0000,0.0037</t>
-  </si>
-  <si>
-    <t>0.3801,0.6667,0.0802,0.0084</t>
-  </si>
-  <si>
-    <t>0.3215,0.7641,0.0134,0.0019</t>
-  </si>
-  <si>
-    <t>0.7055,0.4289,0.0078,0.0011</t>
-  </si>
-  <si>
-    <t>0.7610,0.1254,0.1691,0.0469</t>
-  </si>
-  <si>
-    <t>0.9497,0.0676,0.0056,0.0011</t>
-  </si>
-  <si>
-    <t>0.9529,0.0417,0.0037,0.0016</t>
-  </si>
-  <si>
-    <t>0.9538,0.0993,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.8622,0.2275,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.0060,0.0198,0.9910,0.0003</t>
-  </si>
-  <si>
-    <t>0.9457,0.0557,0.0098,0.0011</t>
-  </si>
-  <si>
-    <t>0.0152,0.0059,0.9876,0.0005</t>
-  </si>
-  <si>
-    <t>0.0036,0.2659,0.9734,0.0039</t>
-  </si>
-  <si>
-    <t>0.3606,0.0375,0.7305,0.0033</t>
-  </si>
-  <si>
-    <t>0.0101,0.0565,0.9670,0.0054</t>
-  </si>
-  <si>
-    <t>0.0118,0.0202,0.9881,0.0004</t>
-  </si>
-  <si>
-    <t>0.0226,0.0012,0.9890,0.0003</t>
-  </si>
-  <si>
-    <t>0.0040,0.0302,0.9919,0.0002</t>
-  </si>
-  <si>
-    <t>0.6361,0.0435,0.3857,0.0315</t>
-  </si>
-  <si>
-    <t>0.6241,0.1178,0.3200,0.0154</t>
-  </si>
-  <si>
-    <t>0.7240,0.0136,0.4448,0.0017</t>
-  </si>
-  <si>
-    <t>0.7125,0.0281,0.4241,0.0029</t>
-  </si>
-  <si>
-    <t>0.4404,0.3459,0.2522,0.0174</t>
-  </si>
-  <si>
-    <t>0.3585,0.0881,0.5377,0.0022</t>
-  </si>
-  <si>
-    <t>0.0814,0.8253,0.0671,0.0688</t>
-  </si>
-  <si>
-    <t>0.5386,0.0178,0.5909,0.0055</t>
-  </si>
-  <si>
-    <t>0.8730,0.1745,0.0093,0.0009</t>
-  </si>
-  <si>
-    <t>0.8892,0.2761,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.8728,0.2114,0.0035,0.0020</t>
-  </si>
-  <si>
-    <t>0.9914,0.0084,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.4046,0.7344,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.6626,0.1599,0.1863,0.0056</t>
-  </si>
-  <si>
-    <t>0.7248,0.0506,0.2722,0.0192</t>
-  </si>
-  <si>
-    <t>0.6230,0.0469,0.0714,0.2761</t>
-  </si>
-  <si>
-    <t>0.3408,0.0247,0.7403,0.0018</t>
-  </si>
-  <si>
-    <t>0.6767,0.0996,0.2564,0.0103</t>
-  </si>
-  <si>
-    <t>0.1903,0.0933,0.7227,0.0216</t>
-  </si>
-  <si>
-    <t>0.0543,0.0681,0.8750,0.0334</t>
-  </si>
-  <si>
-    <t>0.1390,0.0807,0.8367,0.0119</t>
-  </si>
-  <si>
-    <t>0.0931,0.3129,0.5953,0.0201</t>
-  </si>
-  <si>
-    <t>0.0268,0.1019,0.8825,0.0013</t>
-  </si>
-  <si>
-    <t>0.9972,0.0009,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9867,0.0167,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9618,0.0669,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0057,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9919,0.0091,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9928,0.0056,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0003,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9920,0.0016,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.0948,0.0167,0.9445,0.0019</t>
-  </si>
-  <si>
-    <t>0.5864,0.2915,0.2572,0.0597</t>
-  </si>
-  <si>
-    <t>0.9331,0.0465,0.0193,0.0027</t>
-  </si>
-  <si>
-    <t>0.0236,0.0260,0.9653,0.0015</t>
-  </si>
-  <si>
-    <t>0.0127,0.3241,0.8906,0.0029</t>
-  </si>
-  <si>
-    <t>0.0395,0.0139,0.9635,0.0020</t>
-  </si>
-  <si>
-    <t>0.0024,0.0063,0.9941,0.0006</t>
-  </si>
-  <si>
-    <t>0.1938,0.0328,0.7927,0.0019</t>
-  </si>
-  <si>
-    <t>0.0062,0.2468,0.9722,0.0007</t>
-  </si>
-  <si>
-    <t>0.0037,0.1419,0.9782,0.0008</t>
-  </si>
-  <si>
-    <t>0.4831,0.3905,0.1925,0.0564</t>
-  </si>
-  <si>
-    <t>0.5785,0.0442,0.3508,0.1176</t>
-  </si>
-  <si>
-    <t>0.3337,0.0154,0.7584,0.0085</t>
-  </si>
-  <si>
-    <t>0.6178,0.0037,0.1216,0.1878</t>
-  </si>
-  <si>
-    <t>0.9924,0.0097,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0010,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9943,0.0038,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9889,0.0193,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9813,0.0104,0.0014,0.0023</t>
-  </si>
-  <si>
-    <t>0.9866,0.0122,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0019,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0042,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0506,0.3934,0.7323,0.0059</t>
-  </si>
-  <si>
-    <t>0.0141,0.1813,0.9538,0.0020</t>
-  </si>
-  <si>
-    <t>0.0111,0.0290,0.9696,0.0055</t>
-  </si>
-  <si>
-    <t>0.2142,0.0086,0.8720,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.0084,0.9939,0.0027</t>
-  </si>
-  <si>
-    <t>0.4170,0.0192,0.4946,0.1108</t>
-  </si>
-  <si>
-    <t>0.2629,0.0355,0.7203,0.0428</t>
-  </si>
-  <si>
-    <t>0.0961,0.0620,0.8479,0.0273</t>
-  </si>
-  <si>
-    <t>0.7634,0.0111,0.0178,0.2150</t>
-  </si>
-  <si>
-    <t>0.0108,0.3535,0.0040,0.9576</t>
-  </si>
-  <si>
-    <t>0.0157,0.0046,0.0015,0.9907</t>
-  </si>
-  <si>
-    <t>0.0044,0.0010,0.0006,0.9973</t>
-  </si>
-  <si>
-    <t>0.0059,0.0005,0.0010,0.9961</t>
-  </si>
-  <si>
-    <t>0.6336,0.0395,0.0106,0.3847</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8496,0.0377,0.0547,0.0364</t>
+  </si>
+  <si>
+    <t>0.0203,0.0092,0.0011,0.9896</t>
+  </si>
+  <si>
+    <t>0.2965,0.0026,0.0113,0.8282</t>
+  </si>
+  <si>
+    <t>0.0975,0.0122,0.0111,0.9464</t>
+  </si>
+  <si>
+    <t>0.9925,0.0037,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0019,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0008,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9865,0.0170,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9944,0.0037,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9933,0.0017,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9949,0.0008,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.4439,0.2479,0.3146,0.0065</t>
+  </si>
+  <si>
+    <t>0.1269,0.0234,0.9001,0.0020</t>
+  </si>
+  <si>
+    <t>0.2388,0.0090,0.8724,0.0014</t>
+  </si>
+  <si>
+    <t>0.1034,0.1235,0.7613,0.0221</t>
+  </si>
+  <si>
+    <t>0.7967,0.0482,0.2156,0.0035</t>
+  </si>
+  <si>
+    <t>0.0653,0.9513,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.1052,0.9332,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.6564,0.4936,0.0086,0.0010</t>
+  </si>
+  <si>
+    <t>0.4746,0.6874,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.0068,0.9906,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.1577,0.0158,0.8508,0.0138</t>
+  </si>
+  <si>
+    <t>0.4018,0.0239,0.6482,0.0119</t>
+  </si>
+  <si>
+    <t>0.0741,0.0026,0.9629,0.0011</t>
+  </si>
+  <si>
+    <t>0.1168,0.0280,0.8775,0.0035</t>
+  </si>
+  <si>
+    <t>0.1370,0.0195,0.9071,0.0021</t>
+  </si>
+  <si>
+    <t>0.1668,0.0202,0.8321,0.0028</t>
+  </si>
+  <si>
+    <t>0.0330,0.0023,0.9853,0.0004</t>
+  </si>
+  <si>
+    <t>0.1747,0.8980,0.0027,0.0005</t>
+  </si>
+  <si>
+    <t>0.4094,0.1713,0.4425,0.0022</t>
+  </si>
+  <si>
+    <t>0.0055,0.0215,0.9728,0.0126</t>
+  </si>
+  <si>
+    <t>0.0085,0.8988,0.1553,0.0001</t>
+  </si>
+  <si>
+    <t>0.8797,0.0441,0.0334,0.0258</t>
+  </si>
+  <si>
+    <t>0.5830,0.1928,0.2439,0.0097</t>
+  </si>
+  <si>
+    <t>0.6675,0.5172,0.0043,0.0012</t>
+  </si>
+  <si>
+    <t>0.0079,0.9780,0.0508,0.0020</t>
+  </si>
+  <si>
+    <t>0.0476,0.7950,0.1339,0.0692</t>
+  </si>
+  <si>
+    <t>0.0876,0.3743,0.8224,0.0312</t>
+  </si>
+  <si>
+    <t>0.1410,0.1100,0.6870,0.0632</t>
+  </si>
+  <si>
+    <t>0.3305,0.0138,0.4231,0.1984</t>
+  </si>
+  <si>
+    <t>0.0964,0.1026,0.8126,0.0050</t>
+  </si>
+  <si>
+    <t>0.0022,0.9914,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.0467,0.0469,0.9357,0.0015</t>
+  </si>
+  <si>
+    <t>0.2523,0.2070,0.1274,0.6860</t>
+  </si>
+  <si>
+    <t>0.0037,0.9838,0.0146,0.0077</t>
+  </si>
+  <si>
+    <t>0.0179,0.9226,0.2787,0.0120</t>
+  </si>
+  <si>
+    <t>0.0017,0.9905,0.0389,0.0018</t>
+  </si>
+  <si>
+    <t>0.0160,0.4626,0.9013,0.0060</t>
+  </si>
+  <si>
+    <t>0.0009,0.5059,0.9839,0.0003</t>
+  </si>
+  <si>
+    <t>0.1311,0.0501,0.7927,0.0390</t>
+  </si>
+  <si>
+    <t>0.0221,0.0016,0.9787,0.0025</t>
+  </si>
+  <si>
+    <t>0.0154,0.0101,0.9804,0.0022</t>
+  </si>
+  <si>
+    <t>0.0058,0.0748,0.9743,0.0013</t>
+  </si>
+  <si>
+    <t>0.8488,0.2203,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9923,0.0043,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9747,0.0207,0.0052,0.0017</t>
+  </si>
+  <si>
+    <t>0.0462,0.1623,0.9031,0.0227</t>
+  </si>
+  <si>
+    <t>0.9913,0.0040,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9822,0.0247,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9909,0.0028,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.0076,0.8205,0.8048,0.0027</t>
+  </si>
+  <si>
+    <t>0.0232,0.3867,0.9017,0.0090</t>
+  </si>
+  <si>
+    <t>0.0031,0.0460,0.9680,0.0284</t>
+  </si>
+  <si>
+    <t>0.0002,0.9538,0.9710,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.0078,0.9890,0.0006</t>
+  </si>
+  <si>
+    <t>0.0132,0.9568,0.0353,0.0009</t>
+  </si>
+  <si>
+    <t>0.0039,0.9928,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8973,0.0482,0.0769,0.0031</t>
+  </si>
+  <si>
+    <t>0.3227,0.1458,0.6785,0.0120</t>
+  </si>
+  <si>
+    <t>0.0169,0.0862,0.9621,0.0006</t>
+  </si>
+  <si>
+    <t>0.0014,0.9690,0.2683,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.8836,0.7744,0.0031</t>
+  </si>
+  <si>
+    <t>0.0017,0.9862,0.0165,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.8847,0.8356,0.0002</t>
+  </si>
+  <si>
+    <t>0.0529,0.0204,0.0164,0.9604</t>
+  </si>
+  <si>
+    <t>0.0067,0.0007,0.0003,0.9970</t>
+  </si>
+  <si>
+    <t>0.0063,0.0069,0.0027,0.9939</t>
+  </si>
+  <si>
+    <t>0.0047,0.0003,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0013,0.0148,0.0025,0.9975</t>
+  </si>
+  <si>
+    <t>0.0023,0.0152,0.0015,0.9970</t>
+  </si>
+  <si>
+    <t>0.0049,0.9261,0.6176,0.0017</t>
+  </si>
+  <si>
+    <t>0.0015,0.8933,0.9353,0.0003</t>
+  </si>
+  <si>
+    <t>0.0116,0.7006,0.7129,0.0017</t>
+  </si>
+  <si>
+    <t>0.0209,0.5011,0.8122,0.0044</t>
+  </si>
+  <si>
+    <t>0.0021,0.9470,0.5133,0.0006</t>
+  </si>
+  <si>
+    <t>0.0026,0.9421,0.3810,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9943,0.0059,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9939,0.0067,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9925,0.0024,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9862,0.0151,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9935,0.0022,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9810,0.0386,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9760,0.0153,0.0024,0.0021</t>
+  </si>
+  <si>
+    <t>0.9957,0.0017,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9952,0.0031,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0012,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9967,0.0013,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0014,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0014,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.0050,0.0011,0.9898,0.0029</t>
+  </si>
+  <si>
+    <t>0.1459,0.1004,0.7802,0.0163</t>
+  </si>
+  <si>
+    <t>0.5709,0.0828,0.3724,0.0676</t>
+  </si>
+  <si>
+    <t>0.2211,0.0122,0.8413,0.0039</t>
+  </si>
+  <si>
+    <t>0.1142,0.9011,0.0021,0.0023</t>
+  </si>
+  <si>
+    <t>0.0363,0.9490,0.0128,0.0014</t>
+  </si>
+  <si>
+    <t>0.6249,0.5848,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.7036,0.5650,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.1041,0.9226,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.0685,0.9430,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.8748,0.2494,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.2102,0.4807,0.3231,0.0094</t>
+  </si>
+  <si>
+    <t>0.3532,0.0048,0.8375,0.0019</t>
+  </si>
+  <si>
+    <t>0.5029,0.3194,0.2048,0.0173</t>
+  </si>
+  <si>
+    <t>0.5025,0.1071,0.4069,0.0353</t>
+  </si>
+  <si>
+    <t>0.1582,0.5566,0.1927,0.5385</t>
+  </si>
+  <si>
+    <t>0.0044,0.9861,0.0193,0.0030</t>
+  </si>
+  <si>
+    <t>0.0006,0.9941,0.0108,0.0035</t>
+  </si>
+  <si>
+    <t>0.0928,0.8878,0.0149,0.0140</t>
+  </si>
+  <si>
+    <t>0.0002,0.9877,0.6003,0.0001</t>
+  </si>
+  <si>
+    <t>0.1012,0.9137,0.0298,0.0007</t>
+  </si>
+  <si>
+    <t>0.4394,0.5942,0.0309,0.0009</t>
+  </si>
+  <si>
+    <t>0.8245,0.2250,0.0165,0.0087</t>
+  </si>
+  <si>
+    <t>0.9962,0.0031,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9772,0.0068,0.0006,0.0049</t>
+  </si>
+  <si>
+    <t>0.9913,0.0026,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9333,0.0953,0.0046,0.0015</t>
+  </si>
+  <si>
+    <t>0.9958,0.0012,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9781,0.0247,0.0050,0.0001</t>
+  </si>
+  <si>
+    <t>0.9815,0.0042,0.0023,0.0054</t>
+  </si>
+  <si>
+    <t>0.9816,0.0167,0.0035,0.0008</t>
+  </si>
+  <si>
+    <t>0.0012,0.9674,0.4976,0.0003</t>
+  </si>
+  <si>
+    <t>0.0095,0.3916,0.8810,0.0005</t>
+  </si>
+  <si>
+    <t>0.0070,0.6755,0.8016,0.0017</t>
+  </si>
+  <si>
+    <t>0.0511,0.1428,0.7270,0.0008</t>
+  </si>
+  <si>
+    <t>0.7323,0.1108,0.0927,0.0437</t>
+  </si>
+  <si>
+    <t>0.6186,0.2556,0.1387,0.0484</t>
+  </si>
+  <si>
+    <t>0.4454,0.0049,0.7906,0.0027</t>
+  </si>
+  <si>
+    <t>0.7541,0.0594,0.2287,0.0071</t>
+  </si>
+  <si>
+    <t>0.0766,0.0015,0.0021,0.9742</t>
+  </si>
+  <si>
+    <t>0.0009,0.0096,0.0012,0.9982</t>
+  </si>
+  <si>
+    <t>0.0015,0.0550,0.0019,0.9958</t>
+  </si>
+  <si>
+    <t>0.0390,0.0029,0.0019,0.9843</t>
+  </si>
+  <si>
+    <t>0.0093,0.8157,0.7498,0.0021</t>
+  </si>
+  <si>
+    <t>0.9813,0.0054,0.0041,0.0029</t>
+  </si>
+  <si>
+    <t>0.5261,0.6220,0.0017,0.0020</t>
+  </si>
+  <si>
+    <t>0.9645,0.0050,0.0033,0.0149</t>
+  </si>
+  <si>
+    <t>0.8540,0.1828,0.0107,0.0013</t>
+  </si>
+  <si>
+    <t>0.9815,0.0021,0.0008,0.0064</t>
+  </si>
+  <si>
+    <t>0.1095,0.0142,0.0220,0.9263</t>
+  </si>
+  <si>
+    <t>0.9914,0.0009,0.0001,0.0031</t>
+  </si>
+  <si>
+    <t>0.0014,0.2427,0.9647,0.0153</t>
+  </si>
+  <si>
+    <t>0.4143,0.0018,0.0118,0.6984</t>
+  </si>
+  <si>
+    <t>0.8304,0.0100,0.0223,0.1031</t>
+  </si>
+  <si>
+    <t>0.3052,0.7760,0.0146,0.0010</t>
+  </si>
+  <si>
+    <t>0.8887,0.1452,0.0040,0.0025</t>
+  </si>
+  <si>
+    <t>0.9014,0.0779,0.0203,0.0052</t>
+  </si>
+  <si>
+    <t>0.3974,0.4805,0.2030,0.1272</t>
+  </si>
+  <si>
+    <t>0.7365,0.2526,0.0704,0.0226</t>
+  </si>
+  <si>
+    <t>0.8165,0.1994,0.0151,0.0117</t>
+  </si>
+  <si>
+    <t>0.9871,0.0052,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9696,0.0144,0.0057,0.0044</t>
+  </si>
+  <si>
+    <t>0.9938,0.0009,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.9827,0.0003,0.0001,0.0221</t>
+  </si>
+  <si>
+    <t>0.9856,0.0030,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9952,0.0018,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9869,0.0034,0.0005,0.0031</t>
+  </si>
+  <si>
+    <t>0.9925,0.0024,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.6320,0.5388,0.0064,0.0034</t>
+  </si>
+  <si>
+    <t>0.7979,0.3078,0.0045,0.0018</t>
+  </si>
+  <si>
+    <t>0.7997,0.3625,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.8647,0.0514,0.1169,0.0059</t>
+  </si>
+  <si>
+    <t>0.9093,0.2017,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9439,0.0525,0.0138,0.0009</t>
+  </si>
+  <si>
+    <t>0.9510,0.1031,0.0023,0.0002</t>
+  </si>
+  <si>
+    <t>0.9193,0.0825,0.0043,0.0048</t>
+  </si>
+  <si>
+    <t>0.0133,0.0314,0.9856,0.0002</t>
+  </si>
+  <si>
+    <t>0.9545,0.0527,0.0090,0.0008</t>
+  </si>
+  <si>
+    <t>0.0030,0.0193,0.9890,0.0023</t>
+  </si>
+  <si>
+    <t>0.0103,0.2665,0.9598,0.0057</t>
+  </si>
+  <si>
+    <t>0.2120,0.0465,0.7764,0.0043</t>
+  </si>
+  <si>
+    <t>0.0061,0.0989,0.9784,0.0027</t>
+  </si>
+  <si>
+    <t>0.0142,0.0799,0.9498,0.0032</t>
+  </si>
+  <si>
+    <t>0.0078,0.0007,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.0259,0.0305,0.9485,0.0062</t>
+  </si>
+  <si>
+    <t>0.2310,0.1869,0.5738,0.0017</t>
+  </si>
+  <si>
+    <t>0.1265,0.0059,0.9334,0.0014</t>
+  </si>
+  <si>
+    <t>0.3015,0.2074,0.4885,0.0067</t>
+  </si>
+  <si>
+    <t>0.1540,0.4561,0.3877,0.0033</t>
+  </si>
+  <si>
+    <t>0.0280,0.9072,0.0712,0.0032</t>
+  </si>
+  <si>
+    <t>0.5406,0.1271,0.3864,0.0105</t>
+  </si>
+  <si>
+    <t>0.3302,0.5861,0.1172,0.0419</t>
+  </si>
+  <si>
+    <t>0.4062,0.4218,0.1096,0.0595</t>
+  </si>
+  <si>
+    <t>0.9613,0.0551,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.7351,0.4711,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.8831,0.1975,0.0025,0.0013</t>
+  </si>
+  <si>
+    <t>0.8451,0.3242,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.6255,0.5444,0.0051,0.0017</t>
+  </si>
+  <si>
+    <t>0.7804,0.0456,0.1786,0.0080</t>
+  </si>
+  <si>
+    <t>0.8697,0.0078,0.0930,0.0122</t>
+  </si>
+  <si>
+    <t>0.6503,0.0619,0.3069,0.0266</t>
+  </si>
+  <si>
+    <t>0.4938,0.0216,0.6517,0.0058</t>
+  </si>
+  <si>
+    <t>0.6135,0.1243,0.3263,0.0191</t>
+  </si>
+  <si>
+    <t>0.1389,0.0439,0.8693,0.0103</t>
+  </si>
+  <si>
+    <t>0.0021,0.1275,0.9530,0.0294</t>
+  </si>
+  <si>
+    <t>0.0673,0.2442,0.7824,0.0068</t>
+  </si>
+  <si>
+    <t>0.1160,0.3340,0.6477,0.0262</t>
+  </si>
+  <si>
+    <t>0.0237,0.7536,0.4676,0.0119</t>
+  </si>
+  <si>
+    <t>0.9851,0.0083,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.9943,0.0025,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9842,0.0158,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9962,0.0024,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9933,0.0042,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0020,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9916,0.0014,0.0000,0.0017</t>
+  </si>
+  <si>
+    <t>0.9882,0.0113,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.1110,0.0353,0.8909,0.0031</t>
+  </si>
+  <si>
+    <t>0.3307,0.4335,0.2324,0.0025</t>
+  </si>
+  <si>
+    <t>0.9450,0.0286,0.0096,0.0059</t>
+  </si>
+  <si>
+    <t>0.0358,0.0126,0.9584,0.0041</t>
+  </si>
+  <si>
+    <t>0.0016,0.0092,0.9929,0.0012</t>
+  </si>
+  <si>
+    <t>0.0226,0.0426,0.9628,0.0014</t>
+  </si>
+  <si>
+    <t>0.0020,0.0053,0.9903,0.0042</t>
+  </si>
+  <si>
+    <t>0.0968,0.0070,0.9407,0.0020</t>
+  </si>
+  <si>
+    <t>0.0008,0.0149,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.0648,0.0109,0.9552,0.0019</t>
+  </si>
+  <si>
+    <t>0.0624,0.0786,0.9175,0.0082</t>
+  </si>
+  <si>
+    <t>0.5966,0.0211,0.5181,0.0168</t>
+  </si>
+  <si>
+    <t>0.6038,0.0221,0.4924,0.0076</t>
+  </si>
+  <si>
+    <t>0.7224,0.0422,0.2856,0.0216</t>
+  </si>
+  <si>
+    <t>0.9928,0.0035,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9913,0.0071,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9935,0.0069,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9923,0.0121,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9776,0.0136,0.0007,0.0024</t>
+  </si>
+  <si>
+    <t>0.9940,0.0065,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9920,0.0083,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9901,0.0057,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.0208,0.3812,0.6443,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.3433,0.9905,0.0002</t>
+  </si>
+  <si>
+    <t>0.0893,0.1204,0.8421,0.0081</t>
+  </si>
+  <si>
+    <t>0.1414,0.0496,0.8014,0.0160</t>
+  </si>
+  <si>
+    <t>0.0168,0.0319,0.9740,0.0031</t>
+  </si>
+  <si>
+    <t>0.2827,0.0702,0.1227,0.6688</t>
+  </si>
+  <si>
+    <t>0.5460,0.0144,0.5152,0.0285</t>
+  </si>
+  <si>
+    <t>0.0794,0.0602,0.8913,0.0292</t>
+  </si>
+  <si>
+    <t>0.8724,0.0011,0.0042,0.1331</t>
+  </si>
+  <si>
+    <t>0.0338,0.0099,0.0056,0.9810</t>
+  </si>
+  <si>
+    <t>0.0323,0.0049,0.0025,0.9846</t>
+  </si>
+  <si>
+    <t>0.0023,0.0010,0.0053,0.9964</t>
+  </si>
+  <si>
+    <t>0.0063,0.0001,0.0003,0.9973</t>
+  </si>
+  <si>
+    <t>0.8259,0.0223,0.0240,0.0813</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,10 +3491,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,10 +4121,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,10 +4149,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,10 +5423,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
